--- a/rankings.xlsx
+++ b/rankings.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161">

--- a/rankings.xlsx
+++ b/rankings.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="103">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="109">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="141">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="145">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="146">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="149">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="153">
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="158">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="159">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
